--- a/DEV/org.openl.rules.test/test-resources/functionality/properties_all_table_type_allowed.xlsx
+++ b/DEV/org.openl.rules.test/test-resources/functionality/properties_all_table_type_allowed.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="23801"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\EIS_Sources\OpenL\openl-tablets\STUDIO\org.openl.rules.test\test-resources\functionality\"/>
     </mc:Choice>
@@ -223,7 +223,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="786" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="850" uniqueCount="256">
   <si>
     <t>Const1</t>
   </si>
@@ -982,12 +982,22 @@
   </si>
   <si>
     <t>testID14</t>
+  </si>
+  <si>
+    <t>Datatype Vocabulary1 &lt;String&gt;</t>
+  </si>
+  <si>
+    <t>Bla3</t>
+  </si>
+  <si>
+    <t>Bla4</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <numFmts count="0"/>
   <fonts count="18">
     <font>
       <sz val="10"/>
@@ -1215,7 +1225,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="25">
+  <borders count="29">
     <border>
       <left/>
       <right/>
@@ -1493,12 +1503,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1"/>
   </cellStyleXfs>
-  <cellXfs count="126">
+  <cellXfs count="131">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1777,6 +1805,11 @@
     <xf numFmtId="0" fontId="15" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="true"/>
+    <xf numFmtId="14" fontId="6" fillId="4" borderId="16" xfId="0" applyNumberFormat="true" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="14" fontId="6" fillId="4" borderId="16" xfId="0" applyNumberFormat="true" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal 3" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -2147,12 +2180,12 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A3:H455"/>
+  <dimension ref="A3:H470"/>
   <sheetFormatPr defaultRowHeight="12.75" outlineLevelRow="1"/>
   <cols>
-    <col min="2" max="2" width="42.7109375" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="25.42578125" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="28.140625" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" customWidth="true" width="42.7109375" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" width="25.42578125" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" width="28.140625" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:5" collapsed="1">
@@ -4436,110 +4469,19 @@
       </c>
       <c r="D226" s="119"/>
     </row>
-    <row r="228" spans="2:4" collapsed="1">
-      <c r="B228" s="117" t="s">
-        <v>169</v>
-      </c>
-      <c r="C228" s="117"/>
-      <c r="D228" s="117"/>
-    </row>
-    <row r="229" spans="2:4" hidden="1" outlineLevel="1">
-      <c r="B229" s="88" t="s">
-        <v>180</v>
-      </c>
-      <c r="C229" s="52" t="s">
-        <v>222</v>
-      </c>
-      <c r="D229" s="54" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="230" spans="2:4" s="69" customFormat="1" hidden="1" outlineLevel="1">
-      <c r="B230" s="118"/>
-      <c r="C230" s="52" t="s">
-        <v>193</v>
-      </c>
-      <c r="D230" s="58" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="231" spans="2:4" s="69" customFormat="1" hidden="1" outlineLevel="1">
-      <c r="B231" s="118"/>
-      <c r="C231" s="52" t="s">
-        <v>190</v>
-      </c>
-      <c r="D231" s="58" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="232" spans="2:4" s="69" customFormat="1" hidden="1" outlineLevel="1">
-      <c r="B232" s="118"/>
-      <c r="C232" s="52" t="s">
-        <v>188</v>
-      </c>
-      <c r="D232" s="58" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="233" spans="2:4" s="69" customFormat="1" hidden="1" outlineLevel="1">
-      <c r="B233" s="118"/>
-      <c r="C233" s="52" t="s">
-        <v>181</v>
-      </c>
-      <c r="D233" s="58" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="234" spans="2:4" s="69" customFormat="1" hidden="1" outlineLevel="1">
-      <c r="B234" s="118"/>
-      <c r="C234" s="51" t="s">
-        <v>182</v>
-      </c>
-      <c r="D234" s="58" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="235" spans="2:4" s="69" customFormat="1" hidden="1" outlineLevel="1">
-      <c r="B235" s="118"/>
-      <c r="C235" s="52" t="s">
-        <v>183</v>
-      </c>
-      <c r="D235" s="54">
-        <v>41648</v>
-      </c>
-    </row>
-    <row r="236" spans="2:4" hidden="1" outlineLevel="1">
-      <c r="B236" s="88"/>
-      <c r="C236" s="52" t="s">
-        <v>184</v>
-      </c>
-      <c r="D236" s="54">
-        <v>40919</v>
-      </c>
-    </row>
-    <row r="237" spans="2:4" hidden="1" outlineLevel="1">
-      <c r="B237" s="88"/>
-      <c r="C237" s="52" t="s">
-        <v>239</v>
-      </c>
-      <c r="D237" s="50" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="238" spans="2:4" hidden="1" outlineLevel="1">
-      <c r="B238" s="117" t="s">
-        <v>137</v>
-      </c>
-      <c r="C238" s="117"/>
-      <c r="D238" s="117"/>
-    </row>
-    <row r="239" spans="2:4" hidden="1" outlineLevel="1">
-      <c r="B239" s="117" t="s">
-        <v>138</v>
-      </c>
-      <c r="C239" s="117"/>
-      <c r="D239" s="117"/>
-    </row>
+    <row r="228" spans="2:4" collapsed="1"/>
+    <row r="229" spans="2:4" hidden="1" outlineLevel="1"/>
+    <row r="230" spans="2:4" s="69" customFormat="1" hidden="1" outlineLevel="1"/>
+    <row r="231" spans="2:4" s="69" customFormat="1" hidden="1" outlineLevel="1"/>
+    <row r="232" spans="2:4" s="69" customFormat="1" hidden="1" outlineLevel="1"/>
+    <row r="233" spans="2:4" s="69" customFormat="1" hidden="1" outlineLevel="1"/>
+    <row r="234" spans="2:4" s="69" customFormat="1" hidden="1" outlineLevel="1"/>
+    <row r="235" spans="2:4" s="69" customFormat="1" hidden="1" outlineLevel="1"/>
+    <row r="236" spans="2:4" hidden="1" outlineLevel="1"/>
+    <row r="237" spans="2:4" hidden="1" outlineLevel="1"/>
+    <row r="238" spans="2:4" hidden="1" outlineLevel="1"/>
+    <row r="239" spans="2:4" hidden="1" outlineLevel="1"/>
+    <row r="240"/>
     <row r="242" spans="2:5" collapsed="1">
       <c r="B242" s="125" t="s">
         <v>168</v>
@@ -6616,8 +6558,158 @@
       </c>
       <c r="D455" s="102"/>
     </row>
+    <row r="457">
+      <c r="B457" s="117" t="s">
+        <v>253</v>
+      </c>
+      <c r="C457" s="117" t="s">
+        <v>253</v>
+      </c>
+      <c r="D457" s="117" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="B458" s="88" t="s">
+        <v>180</v>
+      </c>
+      <c r="C458" t="s" s="52">
+        <v>222</v>
+      </c>
+      <c r="D458" t="s" s="54">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="B459" s="118" t="s">
+        <v>180</v>
+      </c>
+      <c r="C459" t="s" s="52">
+        <v>193</v>
+      </c>
+      <c r="D459" t="s" s="58">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="B460" s="118" t="s">
+        <v>180</v>
+      </c>
+      <c r="C460" t="s" s="52">
+        <v>190</v>
+      </c>
+      <c r="D460" t="s" s="58">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="B461" s="118" t="s">
+        <v>180</v>
+      </c>
+      <c r="C461" t="s" s="52">
+        <v>188</v>
+      </c>
+      <c r="D461" t="s" s="58">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="B462" s="118" t="s">
+        <v>180</v>
+      </c>
+      <c r="C462" t="s" s="52">
+        <v>181</v>
+      </c>
+      <c r="D462" t="s" s="58">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="B463" s="118" t="s">
+        <v>180</v>
+      </c>
+      <c r="C463" t="s" s="51">
+        <v>182</v>
+      </c>
+      <c r="D463" t="s" s="58">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="B464" s="118" t="s">
+        <v>180</v>
+      </c>
+      <c r="C464" t="s" s="52">
+        <v>183</v>
+      </c>
+      <c r="D464" t="n" s="128">
+        <v>41648.0</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="B465" s="88" t="s">
+        <v>180</v>
+      </c>
+      <c r="C465" t="s" s="52">
+        <v>184</v>
+      </c>
+      <c r="D465" t="n" s="130">
+        <v>40919.0</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="B466" s="88" t="s">
+        <v>180</v>
+      </c>
+      <c r="C466" t="s" s="52">
+        <v>239</v>
+      </c>
+      <c r="D466" t="s" s="50">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="B467" s="117" t="s">
+        <v>135</v>
+      </c>
+      <c r="C467" s="117" t="s">
+        <v>135</v>
+      </c>
+      <c r="D467" s="117" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="B468" s="117" t="s">
+        <v>254</v>
+      </c>
+      <c r="C468" s="117" t="s">
+        <v>254</v>
+      </c>
+      <c r="D468" s="117" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="B469" s="117" t="s">
+        <v>136</v>
+      </c>
+      <c r="C469" s="117" t="s">
+        <v>136</v>
+      </c>
+      <c r="D469" s="117" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="B470" s="117" t="s">
+        <v>255</v>
+      </c>
+      <c r="C470" s="117"/>
+      <c r="D470" s="117"/>
+    </row>
   </sheetData>
-  <mergeCells count="138">
+  <mergeCells count="140">
     <mergeCell ref="C454:D454"/>
     <mergeCell ref="B385:B388"/>
     <mergeCell ref="B359:B366"/>
@@ -6632,15 +6724,12 @@
     <mergeCell ref="D188:E188"/>
     <mergeCell ref="D189:E189"/>
     <mergeCell ref="D190:E190"/>
-    <mergeCell ref="B238:D238"/>
-    <mergeCell ref="B239:D239"/>
     <mergeCell ref="D266:E266"/>
     <mergeCell ref="D267:E267"/>
     <mergeCell ref="D261:E261"/>
     <mergeCell ref="D247:E247"/>
     <mergeCell ref="D248:E248"/>
     <mergeCell ref="D249:E249"/>
-    <mergeCell ref="B229:B237"/>
     <mergeCell ref="B242:E242"/>
     <mergeCell ref="D262:E262"/>
     <mergeCell ref="D192:E192"/>
@@ -6690,7 +6779,6 @@
     <mergeCell ref="B76:F76"/>
     <mergeCell ref="B165:E165"/>
     <mergeCell ref="B4:B30"/>
-    <mergeCell ref="B228:D228"/>
     <mergeCell ref="B216:B224"/>
     <mergeCell ref="C225:D225"/>
     <mergeCell ref="C226:D226"/>
@@ -6756,6 +6844,12 @@
     <mergeCell ref="D255:E255"/>
     <mergeCell ref="D256:E256"/>
     <mergeCell ref="D257:E257"/>
+    <mergeCell ref="B457:D457"/>
+    <mergeCell ref="B458:B466"/>
+    <mergeCell ref="B467:D467"/>
+    <mergeCell ref="B468:D468"/>
+    <mergeCell ref="B469:D469"/>
+    <mergeCell ref="B470:D470"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
